--- a/06_ai-incident-response-playbook-simulation/exercises/starter/incident_response_starter.xlsx
+++ b/06_ai-incident-response-playbook-simulation/exercises/starter/incident_response_starter.xlsx
@@ -50,7 +50,7 @@
       <color rgb="00000000"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -117,6 +117,12 @@
         <bgColor rgb="00FFB6C1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BBDEFB"/>
+        <bgColor rgb="00BBDEFB"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -136,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -179,6 +185,16 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -544,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -676,6 +692,55 @@
       <c r="A17" s="5" t="inlineStr">
         <is>
           <t>• Must report certain incidents to NTSB and FTA within mandated timeframes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>YOUR TASK (Excel):</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>The four working sheets (Incident Playbook, Severity Classification, Reporting Workflow, Post-Incident Review) ship as worked examples. Your job is to REVIEW each row end-to-end and add a team-specific adaptation in the rightmost 'Team Adaptation Notes' column for every row. Notes should call out where your real-world team's context (scale, on-call structure, tooling, regulatory anchor) would deviate from the worked example.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>COLOR LEGEND:</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Blue header — Sheet / column headers</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Light Blue — Pre-filled worked example content — do not modify</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Pink — Your work area: 'Team Adaptation Notes' column — fill these cells</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Green — Scenario description</t>
         </is>
       </c>
     </row>
@@ -701,7 +766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -715,6 +780,7 @@
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
     <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -773,6 +839,11 @@
           <t>Post-Resolution Actions</t>
         </is>
       </c>
+      <c r="L1" s="18" t="inlineStr">
+        <is>
+          <t>Team Adaptation Notes</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="45" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
@@ -830,6 +901,11 @@
           <t>Document root cause; update training pipeline; implement fairness dashboard</t>
         </is>
       </c>
+      <c r="L2" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Model Bias in Route Optimization (S2): does your org have a Fairness or Ethics team separate from the ML team, what fairness dashboard would you actually monitor (e.g., per-ZIP travel-time deltas), and does the S2 1-hour SLA fit a non-safety bias issue versus your equity obligations?]</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
@@ -887,6 +963,11 @@
           <t>Update chatbot guidelines; implement content moderation</t>
         </is>
       </c>
+      <c r="L3" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Offensive Chatbot Responses: who owns content moderation at your org (Trust &amp; Safety, Legal, PR), and is the first-hour 'disable chatbot' authority sitting with on-call engineering or with a separate content team that may be off-hours unreachable?]</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -944,6 +1025,11 @@
           <t>Implement load testing; establish baseline SLAs</t>
         </is>
       </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Performance Degradation Under Load (rush-hour accuracy drop): what is your actual fallback model and is its hand-off automated or manual, and which named SRE/Platform team owns scaling decisions during the S2 1-hour window?]</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -1001,6 +1087,11 @@
           <t>Offer credit monitoring; security audit; improve access controls</t>
         </is>
       </c>
+      <c r="L5" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for a Data Breach of Passenger Info (S1): which named regulator(s) trigger first for your jurisdictions (state breach-notification statute, GDPR Article 33 72-hour clock, CCPA, sector-specific), and who has authority to take the system offline within the 15-minute S1 SLA without exec approval?]</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="45" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
@@ -1058,6 +1149,11 @@
           <t>Establish ground truth verification; add confidence scoring</t>
         </is>
       </c>
+      <c r="L6" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Model Hallucination producing safety-critical wrong guidance (S1): does your org have a 'kill switch' path that bypasses engineering approval, who is empowered to issue the public safety alert, and how do you reach passengers already on the affected route in under 15 minutes?]</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="45" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -1115,6 +1211,11 @@
           <t>Improve change management; add chaos engineering; improve monitoring</t>
         </is>
       </c>
+      <c r="L7" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for a full System Outage (S1): who is your designated Incident Commander rotation, is failover actually tested at the cluster level, and what is your real customer-status-page update cadence during the first hour?]</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -1172,6 +1273,11 @@
           <t>Document compliance framework; implement continuous monitoring</t>
         </is>
       </c>
+      <c r="L8" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for a Regulatory Compliance Violation (S2): which specific regulations apply to your transit-AI deployment (state DOT, FTA, ADA, local data-residency laws), and does Legal or Compliance lead the first-hour response — and do they have a real after-hours pager?]</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
@@ -1236,6 +1342,11 @@
 Reasoning: Adversarial testing identifies similar vulnerabilities proactively; cryptographic verification prevents tampering; threat modeling improves long-term security posture.</t>
         </is>
       </c>
+      <c r="L9" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Adversarial Manipulation of Routing (S1): does your org have a Security Operations Center or is anomaly response owned by ML/Platform, what is your law-enforcement liaison process, and can rate-limiting be enabled by on-call without a change-management ticket?]</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
@@ -1300,6 +1411,11 @@
 Reasoning: Validation gates catch issues early; fingerprinting enables quick identification; access controls limit poisoning opportunities; automated monitoring provides continuous safety.</t>
         </is>
       </c>
+      <c r="L10" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Training Data Poisoning (S1): who owns your data pipeline integrity (Chief Data Officer, Data Platform team, ML Ops), do you actually checksum training batches, and is there an existing 'halt retraining' control that doesn't require redeploying the pipeline?]</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="45" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
@@ -1362,6 +1478,11 @@
         <is>
           <t>"Credential rotation policy; enhanced audit logging; security awareness training; phishing simulations; regular access reviews"
 Reasoning: Regular rotation limits exposure window; audit logging improves detection; training reduces human vulnerabilities; simulations identify at-risk employees; reviews prevent privilege creep.</t>
+        </is>
+      </c>
+      <c r="L11" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Unauthorized System Access (S1): who can revoke API keys and force MFA across the org within 15 minutes, do you have a dormant-account review cadence, and is your secret-rotation tooling automated or a manual runbook step?]</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1386,6 +1507,7 @@
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -1424,6 +1546,11 @@
           <t>Example Incidents</t>
         </is>
       </c>
+      <c r="H1" s="18" t="inlineStr">
+        <is>
+          <t>Team Adaptation Notes</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="45" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
@@ -1461,6 +1588,11 @@
           <t>Data breach; System outage; Safety-critical hallucination</t>
         </is>
       </c>
+      <c r="H2" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for your team's S1 (&lt;15min) on-call: does the SLA actually hold given your geographic spread and weekend coverage, who is the real CEO/Board escalation contact, and is NTSB/FTA notification actually within your org's chain or routed through Legal first?]</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
@@ -1498,6 +1630,11 @@
           <t>Model bias; Performance degradation; Chatbot issues; Adversarial attack</t>
         </is>
       </c>
+      <c r="H3" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for S2 (&lt;1hr): which Slack channels and PagerDuty schedules does your org use, does the named VP-level escalation actually have decision authority during off-hours, and does the 1-hour SLA realistically cover bias incidents that require Fairness-team review?]</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
@@ -1535,6 +1672,11 @@
           <t>Minor accuracy drop; Latency increase; Non-critical bug</t>
         </is>
       </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for S3 (&lt;4hr): does your Engineering Manager rotation actually monitor S3 alerts or do they slip into a backlog, what's the real handoff between on-call and PM ownership, and which channels distinguish S3 from noise so it doesn't get muted?]</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="45" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
@@ -1570,6 +1712,11 @@
       <c r="G5" s="7" t="inlineStr">
         <is>
           <t>UI issue; Documentation error; Slow non-critical query</t>
+        </is>
+      </c>
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for S4 (&lt;24hr): does your team lead actually triage S4 within the day or does it accumulate as tech-debt, is the knowledge-base location standardized, and do you have a rule that prevents S4 from being closed without a written entry?]</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1594,6 +1741,7 @@
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -1632,6 +1780,11 @@
           <t>Output</t>
         </is>
       </c>
+      <c r="H1" s="18" t="inlineStr">
+        <is>
+          <t>Team Adaptation Notes</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="40" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
@@ -1669,6 +1822,11 @@
           <t>Incident ticket created</t>
         </is>
       </c>
+      <c r="H2" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Step 1 Detection: does your team use Prometheus + DataDog or different tools (Grafana, New Relic, Splunk), and what is the real-time-to-5-min SLA gap if monitoring itself degrades during off-hours or during deploys?]</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
@@ -1706,6 +1864,11 @@
           <t>Confirmed incident with initial severity</t>
         </is>
       </c>
+      <c r="H3" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Step 2 Triage: is your On-Call Engineer or Incident Manager the first responder, does PagerDuty actually fire to the right person across time zones, and is the 5-15 min triage window realistic given alert fatigue?]</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -1743,6 +1906,11 @@
           <t>Incident classified with severity and SLA</t>
         </is>
       </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Step 3 Classification: who owns the severity call (Incident Manager vs Tech Lead) and is the classification matrix actually referenced in real incidents, or does severity get debated in Slack and drift?]</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -1780,6 +1948,11 @@
           <t>Incident contained; teams engaged</t>
         </is>
       </c>
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Step 4 Initial Response: what runbook system do you actually use (Confluence, Notion, Git repo), who has author rights, and is the 'war room' virtual (Zoom/Slack huddle) or physical for your distributed team?]</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
@@ -1817,6 +1990,11 @@
           <t>Root cause identified</t>
         </is>
       </c>
+      <c r="H6" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Step 5 Investigation: is your team using ELK or a different stack (Splunk, Datadog APM, OpenSearch), does the 1-48 hour window match your actual MTTR for AI-specific incidents, and how do you keep Data Scientists looped in alongside Engineering and Security?]</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -1854,6 +2032,11 @@
           <t>Fix deployed and verified</t>
         </is>
       </c>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Step 6 Resolution: what is your CI/CD path (GitHub Actions, ArgoCD, Jenkins), do you require staging validation for hotfixes, and who has prod-deploy authority during an active incident?]</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -1891,6 +2074,11 @@
           <t>Resolution verified</t>
         </is>
       </c>
+      <c r="H8" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Step 7 Verification: which monitoring dashboards confirm resolution, is the 1-4 hour post-deploy verification automated or manual, and who signs off as 'verified' — QA, on-call, or Product?]</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
@@ -1928,6 +2116,11 @@
           <t>Customers informed</t>
         </is>
       </c>
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Step 8 Customer Communication: do you use a hosted status page (Statuspage, Instatus), who owns the wording (Product, Comms, Legal), and what's your cadence for updates during an ongoing S1?]</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
@@ -1964,6 +2157,11 @@
           <t>Zoom, Confluence, Jira</t>
         </is>
       </c>
+      <c r="H10" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Step 9 Post-Incident Review: do you actually run blameless postmortems in Confluence or Jira, is the 48-hour window enforced, and does Product or Data Science Lead actually attend or send a delegate?]</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
@@ -1998,6 +2196,11 @@
       <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Confluence, GitHub Wiki</t>
+        </is>
+      </c>
+      <c r="H11" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Step 10 Knowledge Base Update: who owns Confluence/Wiki hygiene at your org, is the 5-business-day window tracked anywhere, and is there an audit to ensure runbook updates and monitoring threshold changes actually ship?]</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2020,6 +2223,7 @@
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -2048,6 +2252,11 @@
           <t>Deadline</t>
         </is>
       </c>
+      <c r="F1" s="18" t="inlineStr">
+        <is>
+          <t>Team Adaptation Notes</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="40" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
@@ -2075,6 +2284,11 @@
           <t>1 day post-incident</t>
         </is>
       </c>
+      <c r="F2" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Incident Timeline: is your Incident Commander a permanent named role or a rotation, do you reconstruct the timeline from PagerDuty/Slack automatically or manually, and is 1 day post-incident realistic for assembling the full chronology?]</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
@@ -2102,6 +2316,11 @@
           <t>3 days post-incident</t>
         </is>
       </c>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Root Cause Analysis: does your org practice blameless PIRs in writing (e.g., does the template include a 'no blame' preamble), and who actually owns the technical RCA — Tech Lead, Principal Engineer, SRE on-call, or ML Lead for model-specific incidents?]</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -2129,6 +2348,11 @@
           <t>2 days post-incident</t>
         </is>
       </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Impact Assessment: does Product or Analytics actually own this at your org, do you have agreed metrics for 'users affected' (sessions, riders, routes), and is 2 days enough to quantify revenue and reputational cost?]</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
@@ -2156,6 +2380,11 @@
           <t>2 days post-incident</t>
         </is>
       </c>
+      <c r="F5" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Response Effectiveness: who scores the team's performance against the runbook (Incident Manager, an external reviewer), and is communication quality assessed objectively or by gut feel?]</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
@@ -2183,6 +2412,11 @@
           <t>3 days post-incident</t>
         </is>
       </c>
+      <c r="F6" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Lessons Learned: how do you actually solicit input from 'All Team Members' (async doc, retro meeting, anonymous form), and does the 3-day deadline survive a busy on-call week?]</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
@@ -2210,6 +2444,11 @@
           <t>5 days post-incident</t>
         </is>
       </c>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Preventive Measures: who has authority to commit to monitoring/process changes (Tech Leads vs Eng Manager budget owners), and how do preventive measures get tracked to completion past the PIR meeting?]</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -2237,6 +2476,11 @@
           <t>5 days post-incident</t>
         </is>
       </c>
+      <c r="F8" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Action Items: is your Project Manager actually staffed to track PIR action items, what tool (Jira, Linear, Asana) holds them, and what's the escalation if action items slip past the deadline?]</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
@@ -2267,6 +2511,11 @@
           <t>2 days post-incident</t>
         </is>
       </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Communication Effectiveness: does your Communications Lead or Customer Relations Director attend the PIR, do you have SLAs for customer updates that you can score against, and is tone-matching evaluated for both internal and external channels?]</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
@@ -2295,6 +2544,11 @@
       <c r="E10" s="7" t="inlineStr">
         <is>
           <t>7 days post-incident</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr">
+        <is>
+          <t>[Your response here — for Follow-up Schedule: who owns the 7-day follow-up (PM or Incident Commander), is there a recurring calendar mechanism to enforce it, and what metric formally closes the loop on 'no recurrence'?]</t>
         </is>
       </c>
     </row>

--- a/06_ai-incident-response-playbook-simulation/exercises/starter/incident_response_starter.xlsx
+++ b/06_ai-incident-response-playbook-simulation/exercises/starter/incident_response_starter.xlsx
@@ -2148,15 +2148,20 @@
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
+          <t>Postmortem Report Template</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Zoom, Confluence, Jira</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>"Postmortem document with timeline, root cause, contributing factors, action items with owners and deadlines"
 Reasoning: Structured documentation ensures completeness; clear ownership and deadlines drive accountability; shared document enables transparency and organizational learning.</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>Zoom, Confluence, Jira</t>
-        </is>
-      </c>
       <c r="H10" s="19" t="inlineStr">
         <is>
           <t>[Your response here — for Step 9 Post-Incident Review: do you actually run blameless postmortems in Confluence or Jira, is the 48-hour window enforced, and does Product or Data Science Lead actually attend or send a delegate?]</t>
@@ -2189,13 +2194,18 @@
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
+          <t>Runbook / KB Update Template</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Confluence, GitHub Wiki</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>"Updated runbooks in Confluence, new alerting rules in monitoring system, root cause article in knowledge base"
 Reasoning: Confluence ensures team can find procedures; updated alerts prevent recurrence; knowledge base article enables transfer of learning across organization.</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>Confluence, GitHub Wiki</t>
         </is>
       </c>
       <c r="H11" s="19" t="inlineStr">
